--- a/ab_meter_output/xlsx/ABMeter_10_16_130_51.xlsx
+++ b/ab_meter_output/xlsx/ABMeter_10_16_130_51.xlsx
@@ -208,12 +208,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$B$2:$B$7</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -240,12 +240,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$C$2:$C$7</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -272,12 +272,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$D$2:$D$7</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$D$2:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -304,12 +304,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$E$2:$E$7</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$E$2:$E$5</f>
             </numRef>
           </val>
         </ser>
@@ -336,12 +336,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$F$2:$F$7</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$F$2:$F$5</f>
             </numRef>
           </val>
         </ser>
@@ -368,12 +368,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$G$2:$G$7</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$G$2:$G$5</f>
             </numRef>
           </val>
         </ser>
@@ -400,12 +400,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$H$2:$H$7</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$H$2:$H$5</f>
             </numRef>
           </val>
         </ser>
@@ -432,12 +432,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$I$2:$I$7</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$I$2:$I$5</f>
             </numRef>
           </val>
         </ser>
@@ -464,12 +464,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$J$2:$J$7</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$J$2:$J$5</f>
             </numRef>
           </val>
         </ser>
@@ -496,12 +496,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$K$2:$K$7</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$K$2:$K$5</f>
             </numRef>
           </val>
         </ser>
@@ -528,12 +528,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$L$2:$L$7</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$L$2:$L$5</f>
             </numRef>
           </val>
         </ser>
@@ -560,12 +560,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$M$2:$M$7</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$M$2:$M$5</f>
             </numRef>
           </val>
         </ser>
@@ -679,12 +679,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'MinMax_Log_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'MinMax_Log_Table'!$B$2:$B$7</f>
+              <f>'MinMax_Log_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'MinMax_Log_Table'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -711,12 +711,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'MinMax_Log_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'MinMax_Log_Table'!$C$2:$C$7</f>
+              <f>'MinMax_Log_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'MinMax_Log_Table'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -743,12 +743,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'MinMax_Log_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'MinMax_Log_Table'!$D$2:$D$7</f>
+              <f>'MinMax_Log_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'MinMax_Log_Table'!$D$2:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -775,12 +775,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'MinMax_Log_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'MinMax_Log_Table'!$E$2:$E$7</f>
+              <f>'MinMax_Log_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'MinMax_Log_Table'!$E$2:$E$5</f>
             </numRef>
           </val>
         </ser>
@@ -807,12 +807,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'MinMax_Log_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'MinMax_Log_Table'!$F$2:$F$7</f>
+              <f>'MinMax_Log_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'MinMax_Log_Table'!$F$2:$F$5</f>
             </numRef>
           </val>
         </ser>
@@ -839,12 +839,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'MinMax_Log_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'MinMax_Log_Table'!$G$2:$G$7</f>
+              <f>'MinMax_Log_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'MinMax_Log_Table'!$G$2:$G$5</f>
             </numRef>
           </val>
         </ser>
@@ -958,12 +958,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$B$2:$B$7</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -990,12 +990,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$C$2:$C$7</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -1022,12 +1022,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$D$2:$D$7</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$D$2:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -1054,12 +1054,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$E$2:$E$7</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$E$2:$E$5</f>
             </numRef>
           </val>
         </ser>
@@ -1086,12 +1086,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$F$2:$F$7</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$F$2:$F$5</f>
             </numRef>
           </val>
         </ser>
@@ -1118,12 +1118,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$G$2:$G$7</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$G$2:$G$5</f>
             </numRef>
           </val>
         </ser>
@@ -1150,12 +1150,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$H$2:$H$7</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$H$2:$H$5</f>
             </numRef>
           </val>
         </ser>
@@ -1182,12 +1182,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$I$2:$I$7</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$I$2:$I$5</f>
             </numRef>
           </val>
         </ser>
@@ -1214,12 +1214,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$J$2:$J$7</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$J$2:$J$5</f>
             </numRef>
           </val>
         </ser>
@@ -1246,12 +1246,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$K$2:$K$7</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$K$2:$K$5</f>
             </numRef>
           </val>
         </ser>
@@ -1278,12 +1278,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$L$2:$L$7</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$L$2:$L$5</f>
             </numRef>
           </val>
         </ser>
@@ -1310,12 +1310,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$M$2:$M$7</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$M$2:$M$5</f>
             </numRef>
           </val>
         </ser>
@@ -1429,12 +1429,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$B$2:$B$7</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -1461,12 +1461,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$C$2:$C$7</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -1493,12 +1493,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$D$2:$D$7</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$D$2:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -1525,12 +1525,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$E$2:$E$7</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$E$2:$E$5</f>
             </numRef>
           </val>
         </ser>
@@ -1557,12 +1557,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$F$2:$F$7</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$F$2:$F$5</f>
             </numRef>
           </val>
         </ser>
@@ -1589,12 +1589,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$G$2:$G$7</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$G$2:$G$5</f>
             </numRef>
           </val>
         </ser>
@@ -1621,12 +1621,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$H$2:$H$7</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$H$2:$H$5</f>
             </numRef>
           </val>
         </ser>
@@ -1653,12 +1653,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$I$2:$I$7</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$I$2:$I$5</f>
             </numRef>
           </val>
         </ser>
@@ -1685,12 +1685,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$J$2:$J$7</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$J$2:$J$5</f>
             </numRef>
           </val>
         </ser>
@@ -1717,12 +1717,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$K$2:$K$7</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$K$2:$K$5</f>
             </numRef>
           </val>
         </ser>
@@ -1749,12 +1749,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$L$2:$L$7</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$L$2:$L$5</f>
             </numRef>
           </val>
         </ser>
@@ -1781,12 +1781,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$M$2:$M$7</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$M$2:$M$5</f>
             </numRef>
           </val>
         </ser>
@@ -1900,12 +1900,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$B$2:$B$7</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -1932,12 +1932,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$C$2:$C$7</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -1964,12 +1964,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$D$2:$D$7</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$D$2:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -1996,12 +1996,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$E$2:$E$7</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$E$2:$E$5</f>
             </numRef>
           </val>
         </ser>
@@ -2028,12 +2028,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$F$2:$F$7</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$F$2:$F$5</f>
             </numRef>
           </val>
         </ser>
@@ -2060,12 +2060,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$G$2:$G$7</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$G$2:$G$5</f>
             </numRef>
           </val>
         </ser>
@@ -2092,12 +2092,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$H$2:$H$7</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$H$2:$H$5</f>
             </numRef>
           </val>
         </ser>
@@ -2124,12 +2124,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$I$2:$I$7</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$I$2:$I$5</f>
             </numRef>
           </val>
         </ser>
@@ -2156,12 +2156,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$J$2:$J$7</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$J$2:$J$5</f>
             </numRef>
           </val>
         </ser>
@@ -2188,12 +2188,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$K$2:$K$7</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$K$2:$K$5</f>
             </numRef>
           </val>
         </ser>
@@ -2220,12 +2220,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$L$2:$L$7</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$L$2:$L$5</f>
             </numRef>
           </val>
         </ser>
@@ -2252,12 +2252,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$M$2:$M$7</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$M$2:$M$5</f>
             </numRef>
           </val>
         </ser>
@@ -2371,12 +2371,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$B$2:$B$7</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -2403,12 +2403,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$C$2:$C$7</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -2435,12 +2435,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$D$2:$D$7</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$D$2:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -2467,12 +2467,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$E$2:$E$7</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$E$2:$E$5</f>
             </numRef>
           </val>
         </ser>
@@ -2499,12 +2499,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$F$2:$F$7</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$F$2:$F$5</f>
             </numRef>
           </val>
         </ser>
@@ -2531,12 +2531,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$G$2:$G$7</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$G$2:$G$5</f>
             </numRef>
           </val>
         </ser>
@@ -2563,12 +2563,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$H$2:$H$7</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$H$2:$H$5</f>
             </numRef>
           </val>
         </ser>
@@ -2595,12 +2595,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$I$2:$I$7</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$I$2:$I$5</f>
             </numRef>
           </val>
         </ser>
@@ -2627,12 +2627,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$J$2:$J$7</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$J$2:$J$5</f>
             </numRef>
           </val>
         </ser>
@@ -2659,12 +2659,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$K$2:$K$7</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$K$2:$K$5</f>
             </numRef>
           </val>
         </ser>
@@ -2691,12 +2691,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$L$2:$L$7</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$L$2:$L$5</f>
             </numRef>
           </val>
         </ser>
@@ -2723,12 +2723,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$M$2:$M$7</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$M$2:$M$5</f>
             </numRef>
           </val>
         </ser>
@@ -2842,12 +2842,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Cumulative_Power_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Cumulative_Power_Table'!$B$2:$B$7</f>
+              <f>'Cumulative_Power_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Cumulative_Power_Table'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -2874,12 +2874,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Cumulative_Power_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Cumulative_Power_Table'!$C$2:$C$7</f>
+              <f>'Cumulative_Power_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Cumulative_Power_Table'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -2906,12 +2906,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Cumulative_Power_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Cumulative_Power_Table'!$D$2:$D$7</f>
+              <f>'Cumulative_Power_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Cumulative_Power_Table'!$D$2:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -2938,12 +2938,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Cumulative_Power_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Cumulative_Power_Table'!$E$2:$E$7</f>
+              <f>'Cumulative_Power_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Cumulative_Power_Table'!$E$2:$E$5</f>
             </numRef>
           </val>
         </ser>
@@ -2970,12 +2970,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Cumulative_Power_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Cumulative_Power_Table'!$F$2:$F$7</f>
+              <f>'Cumulative_Power_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Cumulative_Power_Table'!$F$2:$F$5</f>
             </numRef>
           </val>
         </ser>
@@ -3002,12 +3002,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Cumulative_Power_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Cumulative_Power_Table'!$G$2:$G$7</f>
+              <f>'Cumulative_Power_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Cumulative_Power_Table'!$G$2:$G$5</f>
             </numRef>
           </val>
         </ser>
@@ -3121,12 +3121,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$B$2:$B$7</f>
+              <f>'Demand_Data_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -3153,12 +3153,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$C$2:$C$7</f>
+              <f>'Demand_Data_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -3185,12 +3185,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$D$2:$D$7</f>
+              <f>'Demand_Data_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$D$2:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -3217,12 +3217,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$E$2:$E$7</f>
+              <f>'Demand_Data_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$E$2:$E$5</f>
             </numRef>
           </val>
         </ser>
@@ -3249,12 +3249,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$F$2:$F$7</f>
+              <f>'Demand_Data_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$F$2:$F$5</f>
             </numRef>
           </val>
         </ser>
@@ -3281,12 +3281,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$G$2:$G$7</f>
+              <f>'Demand_Data_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$G$2:$G$5</f>
             </numRef>
           </val>
         </ser>
@@ -3313,12 +3313,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$H$2:$H$7</f>
+              <f>'Demand_Data_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$H$2:$H$5</f>
             </numRef>
           </val>
         </ser>
@@ -3345,12 +3345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$I$2:$I$7</f>
+              <f>'Demand_Data_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$I$2:$I$5</f>
             </numRef>
           </val>
         </ser>
@@ -3377,12 +3377,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$J$2:$J$7</f>
+              <f>'Demand_Data_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$J$2:$J$5</f>
             </numRef>
           </val>
         </ser>
@@ -3409,12 +3409,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$K$2:$K$7</f>
+              <f>'Demand_Data_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$K$2:$K$5</f>
             </numRef>
           </val>
         </ser>
@@ -3441,12 +3441,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$L$2:$L$7</f>
+              <f>'Demand_Data_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$L$2:$L$5</f>
             </numRef>
           </val>
         </ser>
@@ -3473,12 +3473,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$M$2:$M$7</f>
+              <f>'Demand_Data_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$M$2:$M$5</f>
             </numRef>
           </val>
         </ser>
@@ -3592,12 +3592,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$B$2:$B$7</f>
+              <f>'Diagnostic_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -3624,12 +3624,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$C$2:$C$7</f>
+              <f>'Diagnostic_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -3656,12 +3656,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$D$2:$D$7</f>
+              <f>'Diagnostic_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$D$2:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -3688,12 +3688,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$E$2:$E$7</f>
+              <f>'Diagnostic_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$E$2:$E$5</f>
             </numRef>
           </val>
         </ser>
@@ -3720,12 +3720,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$F$2:$F$7</f>
+              <f>'Diagnostic_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$F$2:$F$5</f>
             </numRef>
           </val>
         </ser>
@@ -3752,12 +3752,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$G$2:$G$7</f>
+              <f>'Diagnostic_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$G$2:$G$5</f>
             </numRef>
           </val>
         </ser>
@@ -3784,12 +3784,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$H$2:$H$7</f>
+              <f>'Diagnostic_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$H$2:$H$5</f>
             </numRef>
           </val>
         </ser>
@@ -3816,12 +3816,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$I$2:$I$7</f>
+              <f>'Diagnostic_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$I$2:$I$5</f>
             </numRef>
           </val>
         </ser>
@@ -3848,12 +3848,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$J$2:$J$7</f>
+              <f>'Diagnostic_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$J$2:$J$5</f>
             </numRef>
           </val>
         </ser>
@@ -3880,12 +3880,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$K$2:$K$7</f>
+              <f>'Diagnostic_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$K$2:$K$5</f>
             </numRef>
           </val>
         </ser>
@@ -3912,12 +3912,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$L$2:$L$7</f>
+              <f>'Diagnostic_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$L$2:$L$5</f>
             </numRef>
           </val>
         </ser>
@@ -3944,12 +3944,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$M$2:$M$7</f>
+              <f>'Diagnostic_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$M$2:$M$5</f>
             </numRef>
           </val>
         </ser>
@@ -4063,12 +4063,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$B$2:$B$7</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -4095,12 +4095,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$C$2:$C$7</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -4127,12 +4127,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$D$2:$D$7</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$D$2:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -4159,12 +4159,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$E$2:$E$7</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$E$2:$E$5</f>
             </numRef>
           </val>
         </ser>
@@ -4191,12 +4191,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$F$2:$F$7</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$F$2:$F$5</f>
             </numRef>
           </val>
         </ser>
@@ -4223,12 +4223,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$G$2:$G$7</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$G$2:$G$5</f>
             </numRef>
           </val>
         </ser>
@@ -4255,12 +4255,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$H$2:$H$7</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$H$2:$H$5</f>
             </numRef>
           </val>
         </ser>
@@ -4287,12 +4287,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$I$2:$I$7</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$I$2:$I$5</f>
             </numRef>
           </val>
         </ser>
@@ -4319,12 +4319,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$J$2:$J$7</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$J$2:$J$5</f>
             </numRef>
           </val>
         </ser>
@@ -4351,12 +4351,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$K$2:$K$7</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$K$2:$K$5</f>
             </numRef>
           </val>
         </ser>
@@ -4383,12 +4383,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$L$2:$L$7</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$L$2:$L$5</f>
             </numRef>
           </val>
         </ser>
@@ -4415,12 +4415,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$M$2:$M$7</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$M$2:$M$5</f>
             </numRef>
           </val>
         </ser>
@@ -4534,12 +4534,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$B$2:$B$7</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -4566,12 +4566,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$C$2:$C$7</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -4598,12 +4598,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$D$2:$D$7</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$D$2:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -4630,12 +4630,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$E$2:$E$7</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$E$2:$E$5</f>
             </numRef>
           </val>
         </ser>
@@ -4662,12 +4662,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$F$2:$F$7</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$F$2:$F$5</f>
             </numRef>
           </val>
         </ser>
@@ -4694,12 +4694,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$G$2:$G$7</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$G$2:$G$5</f>
             </numRef>
           </val>
         </ser>
@@ -4726,12 +4726,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$H$2:$H$7</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$H$2:$H$5</f>
             </numRef>
           </val>
         </ser>
@@ -4758,12 +4758,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$I$2:$I$7</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$I$2:$I$5</f>
             </numRef>
           </val>
         </ser>
@@ -4790,12 +4790,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$J$2:$J$7</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$J$2:$J$5</f>
             </numRef>
           </val>
         </ser>
@@ -4822,12 +4822,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$K$2:$K$7</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$K$2:$K$5</f>
             </numRef>
           </val>
         </ser>
@@ -4854,12 +4854,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$L$2:$L$7</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$L$2:$L$5</f>
             </numRef>
           </val>
         </ser>
@@ -4886,12 +4886,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$M$2:$M$7</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$M$2:$M$5</f>
             </numRef>
           </val>
         </ser>
@@ -4966,7 +4966,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5040000"/>
@@ -4993,7 +4993,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5040000"/>
@@ -5020,7 +5020,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5040000"/>
@@ -5047,7 +5047,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5040000"/>
@@ -5074,7 +5074,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5040000"/>
@@ -5101,7 +5101,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5040000"/>
@@ -5128,7 +5128,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5040000"/>
@@ -5155,7 +5155,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5040000"/>
@@ -5182,7 +5182,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5040000"/>
@@ -5209,7 +5209,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5040000"/>
@@ -5236,7 +5236,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5040000"/>
@@ -5546,7 +5546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD7"/>
+  <dimension ref="A1:AD5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -5836,7 +5836,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 11:54:54</t>
+          <t>2026-05-13 12:19:57</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -5930,7 +5930,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 11:55:25</t>
+          <t>2026-05-13 12:20:27</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -6024,7 +6024,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 11:55:56</t>
+          <t>2026-05-13 12:20:58</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -6112,194 +6112,6 @@
         <v>2</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:56:26</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>2399.999756</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>120</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>200</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="W6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD6" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:56:59</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>2399.999756</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>120</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>200</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="U7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="W7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD7" s="3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6315,7 +6127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -6380,7 +6192,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 11:54:54</t>
+          <t>2026-05-13 12:19:57</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -6405,7 +6217,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 11:55:25</t>
+          <t>2026-05-13 12:20:27</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -6430,7 +6242,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 11:55:56</t>
+          <t>2026-05-13 12:20:58</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -6449,56 +6261,6 @@
         <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:56:26</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:56:59</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6514,7 +6276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD7"/>
+  <dimension ref="A1:AD5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -6740,7 +6502,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 11:54:54</t>
+          <t>2026-05-13 12:19:57</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -6834,7 +6596,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 11:55:25</t>
+          <t>2026-05-13 12:20:27</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -6928,7 +6690,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 11:55:56</t>
+          <t>2026-05-13 12:20:58</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -7016,194 +6778,6 @@
         <v>0</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:56:26</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>1403</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>304</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>128</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v>202</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>110</v>
-      </c>
-      <c r="V6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="Z6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="3" t="n">
-        <v>154</v>
-      </c>
-      <c r="AB6" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:56:59</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>1403</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>304</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>128</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v>202</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="3" t="n">
-        <v>110</v>
-      </c>
-      <c r="V7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="Z7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="3" t="n">
-        <v>154</v>
-      </c>
-      <c r="AB7" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7219,7 +6793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -7344,7 +6918,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 11:54:54</t>
+          <t>2026-05-13 12:19:57</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -7393,7 +6967,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 11:55:25</t>
+          <t>2026-05-13 12:20:27</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -7442,7 +7016,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 11:55:56</t>
+          <t>2026-05-13 12:20:58</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -7485,104 +7059,6 @@
         <v>0</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:56:26</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:56:59</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="3" t="n">
         <v>30</v>
       </c>
     </row>
@@ -7598,7 +7074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W7"/>
+  <dimension ref="A1:W5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -7859,71 +7335,71 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 11:54:54</t>
+          <t>2026-05-13 12:19:57</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>19.554668</v>
+        <v>19.22365</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>19.677269</v>
+        <v>19.468849</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>12.51744</v>
+        <v>12.50518</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.004597</v>
+        <v>0.004291</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>17.249792</v>
+        <v>17.065893</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>8.631026</v>
+        <v>8.483907</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>12.92202</v>
+        <v>12.72586</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>149.715912</v>
+        <v>150</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>4339.129395</v>
+        <v>4312.04834</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>4301.908203</v>
+        <v>4280.782227</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>4318.019531</v>
+        <v>4300.712402</v>
       </c>
       <c r="M3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>4319.685547</v>
+        <v>4297.847656</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>4318.813965</v>
+        <v>4297.010254</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>35.505589</v>
+        <v>30.858885</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.822114</v>
+        <v>0.718148</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>2505.169434</v>
+        <v>2492.182617</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>2493.850586</v>
+        <v>2478.599854</v>
       </c>
       <c r="T3" s="3" t="n">
-        <v>2482.055176</v>
+        <v>2472.523438</v>
       </c>
       <c r="U3" s="3" t="n">
-        <v>2493.69165</v>
+        <v>2481.101807</v>
       </c>
       <c r="V3" s="3" t="n">
-        <v>59.992184</v>
+        <v>59.977535</v>
       </c>
       <c r="W3" s="3" t="n">
         <v>2</v>
@@ -7932,71 +7408,71 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 11:55:25</t>
+          <t>2026-05-13 12:20:27</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>20.020548</v>
+        <v>19.039749</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>20.302528</v>
+        <v>19.199129</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.253039</v>
+        <v>12.48066</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0.004597</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>17.858706</v>
+        <v>16.906511</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>8.778146</v>
+        <v>8.336786999999999</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>13.314339</v>
+        <v>12.60326</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>151.67598</v>
+        <v>151.176468</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>4342.217285</v>
+        <v>4312.052246</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>4301.669922</v>
+        <v>4279.824707</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>4317.42334</v>
+        <v>4298.919922</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>4320.437012</v>
+        <v>4296.932129</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>4319.528809</v>
+        <v>4296.057129</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>37.41193</v>
+        <v>31.573763</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.866111</v>
+        <v>0.734947</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>2506.241943</v>
+        <v>2491.706055</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>2495.041992</v>
+        <v>2478.480713</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>2481.221191</v>
+        <v>2471.570312</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>2494.168457</v>
+        <v>2480.585693</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>59.998043</v>
+        <v>59.957027</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>2</v>
@@ -8005,219 +7481,73 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 11:55:56</t>
+          <t>2026-05-13 12:20:58</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>19.346249</v>
+        <v>19.186871</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>19.358509</v>
+        <v>19.43207</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.60326</v>
+        <v>12.84846</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>0.004291</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>17.102673</v>
+        <v>17.155802</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>8.447126000000001</v>
+        <v>8.361307</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>12.774899</v>
+        <v>12.75038</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>151.233673</v>
+        <v>152.492676</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>4342.214355</v>
+        <v>4312.757812</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>4304.893555</v>
+        <v>4279.471191</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>4320.766602</v>
+        <v>4296.775879</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>4322.624512</v>
+        <v>4296.334473</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>4321.673828</v>
+        <v>4295.461426</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>35.386444</v>
+        <v>32.288639</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.818813</v>
+        <v>0.751692</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>2506.718506</v>
+        <v>2491.110352</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>2495.637939</v>
+        <v>2479.076416</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>2483.842285</v>
+        <v>2470.378906</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>2495.399658</v>
+        <v>2480.188477</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>60.012691</v>
+        <v>59.992184</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:56:26</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>19.505629</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>19.79987</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>12.431621</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0.004597</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>17.245707</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>8.680066</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>12.94654</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>149.152542</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>4338.885254</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>4300.599121</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>4316.352051</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>4318.611816</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>4317.741699</v>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v>35.743881</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.827837</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>2504.692871</v>
-      </c>
-      <c r="S6" s="3" t="n">
-        <v>2493.374023</v>
-      </c>
-      <c r="T6" s="3" t="n">
-        <v>2481.102051</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>2493.056396</v>
-      </c>
-      <c r="V6" s="3" t="n">
-        <v>60.023434</v>
-      </c>
-      <c r="W6" s="3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:56:59</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>19.358509</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>19.603708</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>12.21094</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>0.004597</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>17.05772</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>8.631026</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>12.8362</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>148.721588</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>4338.527832</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>4299.04834</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>4314.205078</v>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>4317.260254</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>4316.312012</v>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v>37.173637</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.861236</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>2504.097168</v>
-      </c>
-      <c r="S7" s="3" t="n">
-        <v>2493.135742</v>
-      </c>
-      <c r="T7" s="3" t="n">
-        <v>2479.672119</v>
-      </c>
-      <c r="U7" s="3" t="n">
-        <v>2492.301758</v>
-      </c>
-      <c r="V7" s="3" t="n">
-        <v>60.029293</v>
-      </c>
-      <c r="W7" s="3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -8233,7 +7563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y7"/>
+  <dimension ref="A1:Y5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -8520,396 +7850,238 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 11:54:54</t>
+          <t>2026-05-13 12:19:57</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>14937.318359</v>
+        <v>12534.427734</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>32156.087891</v>
+        <v>29409.353516</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>-16510.607422</v>
+        <v>-14255.425781</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>30582.798828</v>
+        <v>27688.355469</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>47801.195312</v>
+        <v>45851.996094</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>39066.257812</v>
+        <v>37566.824219</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-28336.21875</v>
+        <v>-26799.857422</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>58531.234375</v>
+        <v>56618.960938</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>50121.726562</v>
+        <v>47539.898438</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>50659.554688</v>
+        <v>47741.175781</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>32954</v>
+        <v>30464.632812</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>133735.28125</v>
+        <v>125745.710938</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>-29.802084</v>
+        <v>-26.366121</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>-63.474876</v>
+        <v>-61.60165</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>-50.101986</v>
+        <v>-46.793362</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>-22.646116</v>
+        <v>-22.02039</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>-32.034187</v>
+        <v>-26.183323</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>-64.735985</v>
+        <v>-61.665829</v>
       </c>
       <c r="T3" s="3" t="n">
-        <v>-52.698868</v>
+        <v>-46.64986</v>
       </c>
       <c r="U3" s="3" t="n">
-        <v>99.99884</v>
+        <v>45.429413</v>
       </c>
       <c r="V3" s="3" t="n">
-        <v>99.94266500000001</v>
+        <v>99.93328099999999</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>99.868126</v>
+        <v>99.866264</v>
       </c>
       <c r="X3" s="3" t="n">
-        <v>99.512794</v>
+        <v>99.455978</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>99.774529</v>
+        <v>99.751839</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 11:55:25</t>
+          <t>2026-05-13 12:20:27</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>12844.523438</v>
+        <v>12129.817383</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>29860.800781</v>
+        <v>28145.224609</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>-14486.525391</v>
+        <v>-13728.067383</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>28218.798828</v>
+        <v>26546.976562</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>47129.867188</v>
+        <v>45248.351562</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>38617.988281</v>
+        <v>37213.164062</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>-27866.447266</v>
+        <v>-27128.556641</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>57881.414062</v>
+        <v>55332.960938</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>48883.492188</v>
+        <v>46828.183594</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>48881.4375</v>
+        <v>46698.988281</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>31577.125</v>
+        <v>30509.039062</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>129342.054688</v>
+        <v>124036.210938</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-26.275789</v>
+        <v>-25.902813</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-61.088226</v>
+        <v>-60.269455</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>-45.876644</v>
+        <v>-44.996723</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>-22.144554</v>
+        <v>-21.401566</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>-33.14856</v>
+        <v>-26.183323</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>-65.305305</v>
+        <v>-61.665829</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>-53.434025</v>
+        <v>-46.64986</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>99.990005</v>
+        <v>45.429413</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>99.941605</v>
+        <v>99.93328099999999</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>99.871101</v>
+        <v>99.866264</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>99.530884</v>
+        <v>99.455978</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>99.78119700000001</v>
+        <v>99.751839</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 11:55:56</t>
+          <t>2026-05-13 12:20:58</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>13002.142578</v>
+        <v>14026.757812</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>30350.578125</v>
+        <v>29678.408203</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>-14702.666992</v>
+        <v>-15460.938477</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>28650.050781</v>
+        <v>28244.226562</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>47324.039062</v>
+        <v>45444.019531</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>38706.425781</v>
+        <v>37419.769531</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-27855.509766</v>
+        <v>-27646.005859</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>58174.960938</v>
+        <v>55217.78125</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>49107.859375</v>
+        <v>47587.296875</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>49265.011719</v>
+        <v>47815.6875</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>31703.425781</v>
+        <v>31832.904297</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>130076.296875</v>
+        <v>127235.890625</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-26.476702</v>
+        <v>-29.475843</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-61.606762</v>
+        <v>-62.068352</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>-46.375641</v>
+        <v>-48.569046</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>-21.612633</v>
+        <v>-22.276114</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>-33.14856</v>
+        <v>-26.435194</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-65.305305</v>
+        <v>-61.973316</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-53.434025</v>
+        <v>-47.265442</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>99.990005</v>
+        <v>-99.887108</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>99.941605</v>
+        <v>99.93452499999999</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>99.871101</v>
+        <v>99.865082</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>99.530884</v>
+        <v>99.44972199999999</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>99.78119700000001</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:56:26</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>12055.588867</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>30102.464844</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>-14329.93457</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>27828.121094</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>47113.132812</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>38692.777344</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>-27153.984375</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>58651.921875</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>48638.277344</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>49062.707031</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>30871.486328</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>128572.46875</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-24.786217</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-61.355083</v>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v>-46.418026</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>-21.705215</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>-24.187521</v>
-      </c>
-      <c r="S6" s="3" t="n">
-        <v>-59.828941</v>
-      </c>
-      <c r="T6" s="3" t="n">
-        <v>-43.540813</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>-99.694283</v>
-      </c>
-      <c r="V6" s="3" t="n">
-        <v>99.93369300000001</v>
-      </c>
-      <c r="W6" s="3" t="n">
-        <v>99.849884</v>
-      </c>
-      <c r="X6" s="3" t="n">
-        <v>99.40862300000001</v>
-      </c>
-      <c r="Y6" s="3" t="n">
-        <v>99.73073599999999</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:56:59</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>11356.027344</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>29784.609375</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>-13854.180664</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>27286.457031</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>47071.34375</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>38580.125</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>-26774.148438</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>58877.320312</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>48411.851562</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>48782.996094</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>30276.162109</v>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>127471.007812</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-23.457121</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-61.055313</v>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v>-45.759369</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>-21.398176</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>-24.187521</v>
-      </c>
-      <c r="S7" s="3" t="n">
-        <v>-59.828941</v>
-      </c>
-      <c r="T7" s="3" t="n">
-        <v>-43.540813</v>
-      </c>
-      <c r="U7" s="3" t="n">
-        <v>-99.694283</v>
-      </c>
-      <c r="V7" s="3" t="n">
-        <v>99.93369300000001</v>
-      </c>
-      <c r="W7" s="3" t="n">
-        <v>99.849884</v>
-      </c>
-      <c r="X7" s="3" t="n">
-        <v>99.40862300000001</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v>99.73073599999999</v>
+        <v>99.749779</v>
       </c>
     </row>
   </sheetData>
@@ -8924,7 +8096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -9013,126 +8185,76 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 11:54:54</t>
+          <t>2026-05-13 12:19:57</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>7694573.412228</v>
+        <v>7694584.742669</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>-185.540567</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>7694387.865584</v>
+        <v>7694399.196025</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>19606934.978848</v>
+        <v>19606959.235554</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>-3.179442</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>19606931.796691</v>
+        <v>19606956.053396</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 11:55:25</t>
+          <t>2026-05-13 12:20:27</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>7694573.667771</v>
+        <v>7694584.972552</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>-185.540567</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>7694388.121127</v>
+        <v>7694399.425908</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>19606935.486137</v>
+        <v>19606959.700831</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>-3.179442</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>19606932.303979</v>
+        <v>19606956.518673</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 11:55:56</t>
+          <t>2026-05-13 12:20:58</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>7694573.919358</v>
+        <v>7694585.21365</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>-185.540567</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>7694388.372714</v>
+        <v>7694399.667006</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>19606935.993199</v>
+        <v>19606960.184582</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>-3.179442</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>19606932.811042</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:56:26</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>7694574.155528</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>-185.540567</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>7694388.608884</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>19606936.479221</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>-3.179442</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>19606933.297063</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:56:59</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>7694574.401622</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>-185.540567</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>7694388.854978</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>19606937.003848</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>-3.179442</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>19606933.82169</v>
+        <v>19606957.002424</v>
       </c>
     </row>
   </sheetData>
@@ -9147,7 +8269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -9346,276 +8468,166 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 11:54:54</t>
+          <t>2026-05-13 12:19:57</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>18.193895</v>
+        <v>16.930384</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>28452.589844</v>
+        <v>26830.056641</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>60941.003906</v>
+        <v>58500.984375</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>135901.84375</v>
+        <v>126226.125</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>17.298174</v>
+        <v>16.845064</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>28905.349609</v>
+        <v>27468.087891</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>58285.726562</v>
+        <v>56658.265625</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>129413.21875</v>
+        <v>125584.445312</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>17.419765</v>
+        <v>16.885403</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>29235.826172</v>
+        <v>27570.984375</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>58529.867188</v>
+        <v>56303.5625</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>130350.601562</v>
+        <v>125802.945312</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>17.448717</v>
+        <v>16.888569</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>29192.642578</v>
+        <v>26925.490234</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>58948.699219</v>
+        <v>55329.933594</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>130585.375</v>
+        <v>125969.625</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 11:55:25</t>
+          <t>2026-05-13 12:20:27</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>18.193895</v>
+        <v>16.930384</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>28452.589844</v>
+        <v>26830.056641</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>60941.003906</v>
+        <v>58500.984375</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>135901.84375</v>
+        <v>126226.125</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>17.313986</v>
+        <v>16.85718</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>28945.568359</v>
+        <v>27503.650391</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>58315.328125</v>
+        <v>56616.859375</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>129535.234375</v>
+        <v>125657.023438</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>17.403929</v>
+        <v>17.004322</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>29136.970703</v>
+        <v>28077.533203</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>58553.976562</v>
+        <v>56731.726562</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>130252.242188</v>
+        <v>126647.601562</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>17.399195</v>
+        <v>18.149618</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>28970.455078</v>
+        <v>32995.074219</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>58777.242188</v>
+        <v>59515.640625</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>130305.03125</v>
+        <v>135239.28125</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 11:55:56</t>
+          <t>2026-05-13 12:20:58</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>18.193895</v>
+        <v>16.930384</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>28452.589844</v>
+        <v>26830.056641</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>60941.003906</v>
+        <v>58500.984375</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>135901.84375</v>
+        <v>126226.125</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>17.323395</v>
+        <v>16.87326</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>28958.755859</v>
+        <v>27547.849609</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>58343.972656</v>
+        <v>56569.511719</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>129613.328125</v>
+        <v>125764.109375</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>17.325144</v>
+        <v>17.064043</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>28845.128906</v>
+        <v>28151.140625</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>58317.808594</v>
+        <v>56035.054688</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>129672.265625</v>
+        <v>127088.398438</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>17.125969</v>
+        <v>17.027821</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>28028.140625</v>
+        <v>27866.708984</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>57590.128906</v>
+        <v>49078.902344</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>128240.03125</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:56:26</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>18.193895</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>28452.589844</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>60941.003906</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>135901.84375</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>17.322285</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>28934.142578</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>58350.054688</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>129608.109375</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>17.3146</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>28732.052734</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>58541.191406</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>129562.1875</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>17.397831</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>28594.730469</v>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v>59099.996094</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>130146.765625</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:56:59</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>18.193895</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>28452.589844</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>60941.003906</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>135901.84375</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>17.311403</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>28858.958984</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>58351.757812</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>129527.1875</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>17.245537</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>28458.134766</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>58454.601562</v>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>129032.625</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>17.130016</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>28086.121094</v>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v>58212.605469</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>128158.3125</v>
+        <v>126272.078125</v>
       </c>
     </row>
   </sheetData>
@@ -9630,7 +8642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD7"/>
+  <dimension ref="A1:AD5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -9856,7 +8868,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 11:54:54</t>
+          <t>2026-05-13 12:19:57</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -9950,7 +8962,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 11:55:25</t>
+          <t>2026-05-13 12:20:27</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -10044,7 +9056,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 11:55:56</t>
+          <t>2026-05-13 12:20:58</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -10132,194 +9144,6 @@
         <v>0</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:56:26</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>1403</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>304</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>128</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v>202</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>110</v>
-      </c>
-      <c r="V6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="Z6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="3" t="n">
-        <v>154</v>
-      </c>
-      <c r="AB6" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:56:59</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>1403</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>304</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>128</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v>202</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="3" t="n">
-        <v>110</v>
-      </c>
-      <c r="V7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="Z7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="3" t="n">
-        <v>154</v>
-      </c>
-      <c r="AB7" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10335,7 +9159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z7"/>
+  <dimension ref="A1:Z5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -10617,7 +9441,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 11:54:54</t>
+          <t>2026-05-13 12:19:57</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -10699,7 +9523,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 11:55:25</t>
+          <t>2026-05-13 12:20:27</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -10781,7 +9605,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 11:55:56</t>
+          <t>2026-05-13 12:20:58</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -10857,170 +9681,6 @@
         <v>0</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:56:26</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:56:59</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11036,7 +9696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC7"/>
+  <dimension ref="A1:AC5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -11351,7 +10011,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 11:54:54</t>
+          <t>2026-05-13 12:19:57</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -11442,7 +10102,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 11:55:25</t>
+          <t>2026-05-13 12:20:27</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -11533,7 +10193,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 11:55:56</t>
+          <t>2026-05-13 12:20:58</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -11618,188 +10278,6 @@
         <v>0</v>
       </c>
       <c r="AC5" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:56:26</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:56:59</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="3" t="n">
         <v>0</v>
       </c>
     </row>

--- a/ab_meter_output/xlsx/ABMeter_10_16_130_51.xlsx
+++ b/ab_meter_output/xlsx/ABMeter_10_16_130_51.xlsx
@@ -208,12 +208,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$B$2:$B$5</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$B$2:$B$7</f>
             </numRef>
           </val>
         </ser>
@@ -240,12 +240,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$C$2:$C$5</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$C$2:$C$7</f>
             </numRef>
           </val>
         </ser>
@@ -272,12 +272,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$D$2:$D$5</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$D$2:$D$7</f>
             </numRef>
           </val>
         </ser>
@@ -304,12 +304,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$E$2:$E$5</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$E$2:$E$7</f>
             </numRef>
           </val>
         </ser>
@@ -336,12 +336,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$F$2:$F$5</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$F$2:$F$7</f>
             </numRef>
           </val>
         </ser>
@@ -368,12 +368,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$G$2:$G$5</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$G$2:$G$7</f>
             </numRef>
           </val>
         </ser>
@@ -400,12 +400,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$H$2:$H$5</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$H$2:$H$7</f>
             </numRef>
           </val>
         </ser>
@@ -432,12 +432,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$I$2:$I$5</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$I$2:$I$7</f>
             </numRef>
           </val>
         </ser>
@@ -464,12 +464,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$J$2:$J$5</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$J$2:$J$7</f>
             </numRef>
           </val>
         </ser>
@@ -496,12 +496,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$K$2:$K$5</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$K$2:$K$7</f>
             </numRef>
           </val>
         </ser>
@@ -528,12 +528,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$L$2:$L$5</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$L$2:$L$7</f>
             </numRef>
           </val>
         </ser>
@@ -560,12 +560,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$M$2:$M$5</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$M$2:$M$7</f>
             </numRef>
           </val>
         </ser>
@@ -679,12 +679,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'MinMax_Log_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'MinMax_Log_Table'!$B$2:$B$5</f>
+              <f>'MinMax_Log_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'MinMax_Log_Table'!$B$2:$B$7</f>
             </numRef>
           </val>
         </ser>
@@ -711,12 +711,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'MinMax_Log_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'MinMax_Log_Table'!$C$2:$C$5</f>
+              <f>'MinMax_Log_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'MinMax_Log_Table'!$C$2:$C$7</f>
             </numRef>
           </val>
         </ser>
@@ -743,12 +743,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'MinMax_Log_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'MinMax_Log_Table'!$D$2:$D$5</f>
+              <f>'MinMax_Log_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'MinMax_Log_Table'!$D$2:$D$7</f>
             </numRef>
           </val>
         </ser>
@@ -775,12 +775,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'MinMax_Log_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'MinMax_Log_Table'!$E$2:$E$5</f>
+              <f>'MinMax_Log_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'MinMax_Log_Table'!$E$2:$E$7</f>
             </numRef>
           </val>
         </ser>
@@ -807,12 +807,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'MinMax_Log_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'MinMax_Log_Table'!$F$2:$F$5</f>
+              <f>'MinMax_Log_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'MinMax_Log_Table'!$F$2:$F$7</f>
             </numRef>
           </val>
         </ser>
@@ -839,12 +839,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'MinMax_Log_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'MinMax_Log_Table'!$G$2:$G$5</f>
+              <f>'MinMax_Log_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'MinMax_Log_Table'!$G$2:$G$7</f>
             </numRef>
           </val>
         </ser>
@@ -958,12 +958,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$B$2:$B$5</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$B$2:$B$7</f>
             </numRef>
           </val>
         </ser>
@@ -990,12 +990,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$C$2:$C$5</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$C$2:$C$7</f>
             </numRef>
           </val>
         </ser>
@@ -1022,12 +1022,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$D$2:$D$5</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$D$2:$D$7</f>
             </numRef>
           </val>
         </ser>
@@ -1054,12 +1054,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$E$2:$E$5</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$E$2:$E$7</f>
             </numRef>
           </val>
         </ser>
@@ -1086,12 +1086,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$F$2:$F$5</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$F$2:$F$7</f>
             </numRef>
           </val>
         </ser>
@@ -1118,12 +1118,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$G$2:$G$5</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$G$2:$G$7</f>
             </numRef>
           </val>
         </ser>
@@ -1150,12 +1150,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$H$2:$H$5</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$H$2:$H$7</f>
             </numRef>
           </val>
         </ser>
@@ -1182,12 +1182,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$I$2:$I$5</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$I$2:$I$7</f>
             </numRef>
           </val>
         </ser>
@@ -1214,12 +1214,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$J$2:$J$5</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$J$2:$J$7</f>
             </numRef>
           </val>
         </ser>
@@ -1246,12 +1246,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$K$2:$K$5</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$K$2:$K$7</f>
             </numRef>
           </val>
         </ser>
@@ -1278,12 +1278,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$L$2:$L$5</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$L$2:$L$7</f>
             </numRef>
           </val>
         </ser>
@@ -1310,12 +1310,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$M$2:$M$5</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$M$2:$M$7</f>
             </numRef>
           </val>
         </ser>
@@ -1429,12 +1429,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$B$2:$B$5</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$B$2:$B$7</f>
             </numRef>
           </val>
         </ser>
@@ -1461,12 +1461,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$C$2:$C$5</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$C$2:$C$7</f>
             </numRef>
           </val>
         </ser>
@@ -1493,12 +1493,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$D$2:$D$5</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$D$2:$D$7</f>
             </numRef>
           </val>
         </ser>
@@ -1525,12 +1525,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$E$2:$E$5</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$E$2:$E$7</f>
             </numRef>
           </val>
         </ser>
@@ -1557,12 +1557,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$F$2:$F$5</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$F$2:$F$7</f>
             </numRef>
           </val>
         </ser>
@@ -1589,12 +1589,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$G$2:$G$5</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$G$2:$G$7</f>
             </numRef>
           </val>
         </ser>
@@ -1621,12 +1621,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$H$2:$H$5</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$H$2:$H$7</f>
             </numRef>
           </val>
         </ser>
@@ -1653,12 +1653,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$I$2:$I$5</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$I$2:$I$7</f>
             </numRef>
           </val>
         </ser>
@@ -1685,12 +1685,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$J$2:$J$5</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$J$2:$J$7</f>
             </numRef>
           </val>
         </ser>
@@ -1717,12 +1717,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$K$2:$K$5</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$K$2:$K$7</f>
             </numRef>
           </val>
         </ser>
@@ -1749,12 +1749,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$L$2:$L$5</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$L$2:$L$7</f>
             </numRef>
           </val>
         </ser>
@@ -1781,12 +1781,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$M$2:$M$5</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$M$2:$M$7</f>
             </numRef>
           </val>
         </ser>
@@ -1900,12 +1900,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$B$2:$B$5</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$B$2:$B$7</f>
             </numRef>
           </val>
         </ser>
@@ -1932,12 +1932,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$C$2:$C$5</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$C$2:$C$7</f>
             </numRef>
           </val>
         </ser>
@@ -1964,12 +1964,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$D$2:$D$5</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$D$2:$D$7</f>
             </numRef>
           </val>
         </ser>
@@ -1996,12 +1996,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$E$2:$E$5</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$E$2:$E$7</f>
             </numRef>
           </val>
         </ser>
@@ -2028,12 +2028,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$F$2:$F$5</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$F$2:$F$7</f>
             </numRef>
           </val>
         </ser>
@@ -2060,12 +2060,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$G$2:$G$5</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$G$2:$G$7</f>
             </numRef>
           </val>
         </ser>
@@ -2092,12 +2092,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$H$2:$H$5</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$H$2:$H$7</f>
             </numRef>
           </val>
         </ser>
@@ -2124,12 +2124,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$I$2:$I$5</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$I$2:$I$7</f>
             </numRef>
           </val>
         </ser>
@@ -2156,12 +2156,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$J$2:$J$5</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$J$2:$J$7</f>
             </numRef>
           </val>
         </ser>
@@ -2188,12 +2188,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$K$2:$K$5</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$K$2:$K$7</f>
             </numRef>
           </val>
         </ser>
@@ -2220,12 +2220,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$L$2:$L$5</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$L$2:$L$7</f>
             </numRef>
           </val>
         </ser>
@@ -2252,12 +2252,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$M$2:$M$5</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$M$2:$M$7</f>
             </numRef>
           </val>
         </ser>
@@ -2371,12 +2371,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$B$2:$B$5</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$B$2:$B$7</f>
             </numRef>
           </val>
         </ser>
@@ -2403,12 +2403,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$C$2:$C$5</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$C$2:$C$7</f>
             </numRef>
           </val>
         </ser>
@@ -2435,12 +2435,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$D$2:$D$5</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$D$2:$D$7</f>
             </numRef>
           </val>
         </ser>
@@ -2467,12 +2467,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$E$2:$E$5</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$E$2:$E$7</f>
             </numRef>
           </val>
         </ser>
@@ -2499,12 +2499,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$F$2:$F$5</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$F$2:$F$7</f>
             </numRef>
           </val>
         </ser>
@@ -2531,12 +2531,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$G$2:$G$5</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$G$2:$G$7</f>
             </numRef>
           </val>
         </ser>
@@ -2563,12 +2563,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$H$2:$H$5</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$H$2:$H$7</f>
             </numRef>
           </val>
         </ser>
@@ -2595,12 +2595,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$I$2:$I$5</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$I$2:$I$7</f>
             </numRef>
           </val>
         </ser>
@@ -2627,12 +2627,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$J$2:$J$5</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$J$2:$J$7</f>
             </numRef>
           </val>
         </ser>
@@ -2659,12 +2659,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$K$2:$K$5</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$K$2:$K$7</f>
             </numRef>
           </val>
         </ser>
@@ -2691,12 +2691,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$L$2:$L$5</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$L$2:$L$7</f>
             </numRef>
           </val>
         </ser>
@@ -2723,12 +2723,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$M$2:$M$5</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$M$2:$M$7</f>
             </numRef>
           </val>
         </ser>
@@ -2842,12 +2842,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Cumulative_Power_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Cumulative_Power_Table'!$B$2:$B$5</f>
+              <f>'Cumulative_Power_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Cumulative_Power_Table'!$B$2:$B$7</f>
             </numRef>
           </val>
         </ser>
@@ -2874,12 +2874,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Cumulative_Power_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Cumulative_Power_Table'!$C$2:$C$5</f>
+              <f>'Cumulative_Power_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Cumulative_Power_Table'!$C$2:$C$7</f>
             </numRef>
           </val>
         </ser>
@@ -2906,12 +2906,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Cumulative_Power_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Cumulative_Power_Table'!$D$2:$D$5</f>
+              <f>'Cumulative_Power_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Cumulative_Power_Table'!$D$2:$D$7</f>
             </numRef>
           </val>
         </ser>
@@ -2938,12 +2938,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Cumulative_Power_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Cumulative_Power_Table'!$E$2:$E$5</f>
+              <f>'Cumulative_Power_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Cumulative_Power_Table'!$E$2:$E$7</f>
             </numRef>
           </val>
         </ser>
@@ -2970,12 +2970,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Cumulative_Power_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Cumulative_Power_Table'!$F$2:$F$5</f>
+              <f>'Cumulative_Power_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Cumulative_Power_Table'!$F$2:$F$7</f>
             </numRef>
           </val>
         </ser>
@@ -3002,12 +3002,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Cumulative_Power_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Cumulative_Power_Table'!$G$2:$G$5</f>
+              <f>'Cumulative_Power_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Cumulative_Power_Table'!$G$2:$G$7</f>
             </numRef>
           </val>
         </ser>
@@ -3121,12 +3121,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$B$2:$B$5</f>
+              <f>'Demand_Data_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$B$2:$B$7</f>
             </numRef>
           </val>
         </ser>
@@ -3153,12 +3153,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$C$2:$C$5</f>
+              <f>'Demand_Data_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$C$2:$C$7</f>
             </numRef>
           </val>
         </ser>
@@ -3185,12 +3185,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$D$2:$D$5</f>
+              <f>'Demand_Data_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$D$2:$D$7</f>
             </numRef>
           </val>
         </ser>
@@ -3217,12 +3217,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$E$2:$E$5</f>
+              <f>'Demand_Data_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$E$2:$E$7</f>
             </numRef>
           </val>
         </ser>
@@ -3249,12 +3249,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$F$2:$F$5</f>
+              <f>'Demand_Data_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$F$2:$F$7</f>
             </numRef>
           </val>
         </ser>
@@ -3281,12 +3281,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$G$2:$G$5</f>
+              <f>'Demand_Data_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$G$2:$G$7</f>
             </numRef>
           </val>
         </ser>
@@ -3313,12 +3313,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$H$2:$H$5</f>
+              <f>'Demand_Data_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$H$2:$H$7</f>
             </numRef>
           </val>
         </ser>
@@ -3345,12 +3345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$I$2:$I$5</f>
+              <f>'Demand_Data_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$I$2:$I$7</f>
             </numRef>
           </val>
         </ser>
@@ -3377,12 +3377,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$J$2:$J$5</f>
+              <f>'Demand_Data_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$J$2:$J$7</f>
             </numRef>
           </val>
         </ser>
@@ -3409,12 +3409,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$K$2:$K$5</f>
+              <f>'Demand_Data_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$K$2:$K$7</f>
             </numRef>
           </val>
         </ser>
@@ -3441,12 +3441,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$L$2:$L$5</f>
+              <f>'Demand_Data_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$L$2:$L$7</f>
             </numRef>
           </val>
         </ser>
@@ -3473,12 +3473,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$M$2:$M$5</f>
+              <f>'Demand_Data_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$M$2:$M$7</f>
             </numRef>
           </val>
         </ser>
@@ -3592,12 +3592,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$B$2:$B$5</f>
+              <f>'Diagnostic_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$B$2:$B$7</f>
             </numRef>
           </val>
         </ser>
@@ -3624,12 +3624,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$C$2:$C$5</f>
+              <f>'Diagnostic_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$C$2:$C$7</f>
             </numRef>
           </val>
         </ser>
@@ -3656,12 +3656,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$D$2:$D$5</f>
+              <f>'Diagnostic_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$D$2:$D$7</f>
             </numRef>
           </val>
         </ser>
@@ -3688,12 +3688,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$E$2:$E$5</f>
+              <f>'Diagnostic_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$E$2:$E$7</f>
             </numRef>
           </val>
         </ser>
@@ -3720,12 +3720,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$F$2:$F$5</f>
+              <f>'Diagnostic_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$F$2:$F$7</f>
             </numRef>
           </val>
         </ser>
@@ -3752,12 +3752,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$G$2:$G$5</f>
+              <f>'Diagnostic_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$G$2:$G$7</f>
             </numRef>
           </val>
         </ser>
@@ -3784,12 +3784,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$H$2:$H$5</f>
+              <f>'Diagnostic_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$H$2:$H$7</f>
             </numRef>
           </val>
         </ser>
@@ -3816,12 +3816,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$I$2:$I$5</f>
+              <f>'Diagnostic_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$I$2:$I$7</f>
             </numRef>
           </val>
         </ser>
@@ -3848,12 +3848,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$J$2:$J$5</f>
+              <f>'Diagnostic_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$J$2:$J$7</f>
             </numRef>
           </val>
         </ser>
@@ -3880,12 +3880,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$K$2:$K$5</f>
+              <f>'Diagnostic_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$K$2:$K$7</f>
             </numRef>
           </val>
         </ser>
@@ -3912,12 +3912,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$L$2:$L$5</f>
+              <f>'Diagnostic_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$L$2:$L$7</f>
             </numRef>
           </val>
         </ser>
@@ -3944,12 +3944,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$M$2:$M$5</f>
+              <f>'Diagnostic_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$M$2:$M$7</f>
             </numRef>
           </val>
         </ser>
@@ -4063,12 +4063,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$B$2:$B$5</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$B$2:$B$7</f>
             </numRef>
           </val>
         </ser>
@@ -4095,12 +4095,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$C$2:$C$5</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$C$2:$C$7</f>
             </numRef>
           </val>
         </ser>
@@ -4127,12 +4127,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$D$2:$D$5</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$D$2:$D$7</f>
             </numRef>
           </val>
         </ser>
@@ -4159,12 +4159,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$E$2:$E$5</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$E$2:$E$7</f>
             </numRef>
           </val>
         </ser>
@@ -4191,12 +4191,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$F$2:$F$5</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$F$2:$F$7</f>
             </numRef>
           </val>
         </ser>
@@ -4223,12 +4223,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$G$2:$G$5</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$G$2:$G$7</f>
             </numRef>
           </val>
         </ser>
@@ -4255,12 +4255,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$H$2:$H$5</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$H$2:$H$7</f>
             </numRef>
           </val>
         </ser>
@@ -4287,12 +4287,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$I$2:$I$5</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$I$2:$I$7</f>
             </numRef>
           </val>
         </ser>
@@ -4319,12 +4319,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$J$2:$J$5</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$J$2:$J$7</f>
             </numRef>
           </val>
         </ser>
@@ -4351,12 +4351,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$K$2:$K$5</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$K$2:$K$7</f>
             </numRef>
           </val>
         </ser>
@@ -4383,12 +4383,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$L$2:$L$5</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$L$2:$L$7</f>
             </numRef>
           </val>
         </ser>
@@ -4415,12 +4415,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$M$2:$M$5</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$M$2:$M$7</f>
             </numRef>
           </val>
         </ser>
@@ -4534,12 +4534,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$B$2:$B$5</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$B$2:$B$7</f>
             </numRef>
           </val>
         </ser>
@@ -4566,12 +4566,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$C$2:$C$5</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$C$2:$C$7</f>
             </numRef>
           </val>
         </ser>
@@ -4598,12 +4598,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$D$2:$D$5</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$D$2:$D$7</f>
             </numRef>
           </val>
         </ser>
@@ -4630,12 +4630,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$E$2:$E$5</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$E$2:$E$7</f>
             </numRef>
           </val>
         </ser>
@@ -4662,12 +4662,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$F$2:$F$5</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$F$2:$F$7</f>
             </numRef>
           </val>
         </ser>
@@ -4694,12 +4694,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$G$2:$G$5</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$G$2:$G$7</f>
             </numRef>
           </val>
         </ser>
@@ -4726,12 +4726,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$H$2:$H$5</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$H$2:$H$7</f>
             </numRef>
           </val>
         </ser>
@@ -4758,12 +4758,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$I$2:$I$5</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$I$2:$I$7</f>
             </numRef>
           </val>
         </ser>
@@ -4790,12 +4790,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$J$2:$J$5</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$J$2:$J$7</f>
             </numRef>
           </val>
         </ser>
@@ -4822,12 +4822,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$K$2:$K$5</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$K$2:$K$7</f>
             </numRef>
           </val>
         </ser>
@@ -4854,12 +4854,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$L$2:$L$5</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$L$2:$L$7</f>
             </numRef>
           </val>
         </ser>
@@ -4886,12 +4886,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$M$2:$M$5</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$M$2:$M$7</f>
             </numRef>
           </val>
         </ser>
@@ -4966,7 +4966,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5040000"/>
@@ -4993,7 +4993,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5040000"/>
@@ -5020,7 +5020,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5040000"/>
@@ -5047,7 +5047,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5040000"/>
@@ -5074,7 +5074,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5040000"/>
@@ -5101,7 +5101,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5040000"/>
@@ -5128,7 +5128,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5040000"/>
@@ -5155,7 +5155,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5040000"/>
@@ -5182,7 +5182,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5040000"/>
@@ -5209,7 +5209,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5040000"/>
@@ -5236,7 +5236,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5040000"/>
@@ -5546,7 +5546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD5"/>
+  <dimension ref="A1:AD7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -5836,7 +5836,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 12:19:57</t>
+          <t>2026-05-13 12:35:18</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -5930,7 +5930,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 12:20:27</t>
+          <t>2026-05-13 12:35:33</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -6024,7 +6024,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 12:20:58</t>
+          <t>2026-05-13 12:35:49</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -6112,6 +6112,194 @@
         <v>2</v>
       </c>
       <c r="AD5" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:36:04</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>2399.999756</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD6" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:36:19</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>2399.999756</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD7" s="3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6127,7 +6315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -6192,7 +6380,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 12:19:57</t>
+          <t>2026-05-13 12:35:18</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -6217,7 +6405,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 12:20:27</t>
+          <t>2026-05-13 12:35:33</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -6242,7 +6430,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 12:20:58</t>
+          <t>2026-05-13 12:35:49</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -6261,6 +6449,56 @@
         <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:36:04</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:36:19</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6276,7 +6514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD5"/>
+  <dimension ref="A1:AD7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -6502,7 +6740,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 12:19:57</t>
+          <t>2026-05-13 12:35:18</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -6596,7 +6834,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 12:20:27</t>
+          <t>2026-05-13 12:35:33</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -6690,7 +6928,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 12:20:58</t>
+          <t>2026-05-13 12:35:49</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -6778,6 +7016,194 @@
         <v>0</v>
       </c>
       <c r="AD5" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:36:04</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>1403</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>304</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>202</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="3" t="n">
+        <v>154</v>
+      </c>
+      <c r="AB6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:36:19</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>1403</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>304</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>202</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="3" t="n">
+        <v>154</v>
+      </c>
+      <c r="AB7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6793,7 +7219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -6918,7 +7344,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 12:19:57</t>
+          <t>2026-05-13 12:35:18</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -6967,7 +7393,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 12:20:27</t>
+          <t>2026-05-13 12:35:33</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -7016,7 +7442,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 12:20:58</t>
+          <t>2026-05-13 12:35:49</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -7059,6 +7485,104 @@
         <v>0</v>
       </c>
       <c r="O5" s="3" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:36:04</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:36:19</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="3" t="n">
         <v>30</v>
       </c>
     </row>
@@ -7074,7 +7598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W5"/>
+  <dimension ref="A1:W7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -7335,71 +7859,71 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 12:19:57</t>
+          <t>2026-05-13 12:35:18</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>19.22365</v>
+        <v>21.405926</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>19.468849</v>
+        <v>22.166044</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>12.50518</v>
+        <v>14.442257</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.004291</v>
+        <v>0.004597</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>17.065893</v>
+        <v>19.338076</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>8.483907</v>
+        <v>9.440186000000001</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>12.72586</v>
+        <v>14.393217</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>150</v>
+        <v>152.467529</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>4312.04834</v>
+        <v>4332.708984</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>4280.782227</v>
+        <v>4298.211914</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>4300.712402</v>
+        <v>4314.562012</v>
       </c>
       <c r="M3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>4297.847656</v>
+        <v>4315.160645</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>4297.010254</v>
+        <v>4314.286621</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>30.858885</v>
+        <v>33.360958</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.718148</v>
+        <v>0.773267</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>2492.182617</v>
+        <v>2502.071777</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>2478.599854</v>
+        <v>2490.514648</v>
       </c>
       <c r="T3" s="3" t="n">
-        <v>2472.523438</v>
+        <v>2480.625488</v>
       </c>
       <c r="U3" s="3" t="n">
-        <v>2481.101807</v>
+        <v>2491.070557</v>
       </c>
       <c r="V3" s="3" t="n">
-        <v>59.977535</v>
+        <v>60.020504</v>
       </c>
       <c r="W3" s="3" t="n">
         <v>2</v>
@@ -7408,71 +7932,71 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 12:20:27</t>
+          <t>2026-05-13 12:35:33</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>19.039749</v>
+        <v>21.626606</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>19.199129</v>
+        <v>22.533844</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>12.48066</v>
+        <v>14.344177</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0.004597</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>16.906511</v>
+        <v>19.501543</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>8.336786999999999</v>
+        <v>9.648604000000001</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>12.60326</v>
+        <v>14.564857</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>151.176468</v>
+        <v>150.952988</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>4312.052246</v>
+        <v>4326.887207</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>4279.824707</v>
+        <v>4294.750977</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>4298.919922</v>
+        <v>4309.907715</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>4296.932129</v>
+        <v>4310.515625</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>4296.057129</v>
+        <v>4309.639648</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>31.573763</v>
+        <v>31.931202</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.734947</v>
+        <v>0.7409249999999999</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>2491.706055</v>
+        <v>2498.616455</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>2478.480713</v>
+        <v>2487.893311</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>2471.570312</v>
+        <v>2478.599854</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>2480.585693</v>
+        <v>2488.369873</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>59.957027</v>
+        <v>60.023434</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>2</v>
@@ -7481,73 +8005,219 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 12:20:58</t>
+          <t>2026-05-13 12:35:49</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>19.186871</v>
+        <v>21.589827</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>19.43207</v>
+        <v>22.448025</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.84846</v>
+        <v>14.331918</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.004291</v>
+        <v>0.004597</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>17.155802</v>
+        <v>19.456589</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>8.361307</v>
+        <v>9.611825</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>12.75038</v>
+        <v>14.515817</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>152.492676</v>
+        <v>151.020401</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>4312.757812</v>
+        <v>4326.411621</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>4279.471191</v>
+        <v>4293.199707</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>4296.775879</v>
+        <v>4310.743652</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>4296.334473</v>
+        <v>4310.118652</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>4295.461426</v>
+        <v>4309.282227</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>32.288639</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.751692</v>
+        <v>0.749281</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>2491.110352</v>
+        <v>2499.093018</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>2479.076416</v>
+        <v>2486.821045</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>2470.378906</v>
+        <v>2478.480713</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>2480.188477</v>
+        <v>2488.131592</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>59.992184</v>
+        <v>60.026363</v>
       </c>
       <c r="W5" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:36:04</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>21.307846</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>22.031185</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>14.393217</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0.004597</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>19.244081</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>9.391145</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>14.319657</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>152.480423</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>4324.750488</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>4290.931641</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>4309.071777</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>4308.251465</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>4307.375977</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>32.64608</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.757911</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>2498.259033</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>2485.748779</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>2477.051025</v>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>2487.019531</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>60.017574</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:36:19</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>21.589827</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>22.484804</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>14.626157</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0.004291</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>19.566929</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>9.550525</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>14.564857</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>152.503204</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>4324.274902</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>4292.363281</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>4308.952637</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>4308.530762</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>4307.614258</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>31.692909</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.735742</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>2497.782471</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>2486.106201</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>2477.765869</v>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>2487.218018</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>60.017574</v>
+      </c>
+      <c r="W7" s="3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7563,7 +8233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y5"/>
+  <dimension ref="A1:Y7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -7850,238 +8520,396 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 12:19:57</t>
+          <t>2026-05-13 12:35:18</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>12534.427734</v>
+        <v>12998.02832</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>29409.353516</v>
+        <v>33183.695312</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>-14255.425781</v>
+        <v>-16949.527344</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>27688.355469</v>
+        <v>29232.195312</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>45851.996094</v>
+        <v>52436.175781</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>37566.824219</v>
+        <v>44996.6875</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-26799.857422</v>
+        <v>-31331.910156</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>56618.960938</v>
+        <v>66100.953125</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>47539.898438</v>
+        <v>54014.140625</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>47741.175781</v>
+        <v>55937.632812</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>30464.632812</v>
+        <v>35739.71875</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>125745.710938</v>
+        <v>145691.5</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>-26.366121</v>
+        <v>-24.064121</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>-61.60165</v>
+        <v>-59.32267</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>-46.793362</v>
+        <v>-47.424908</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>-22.02039</v>
+        <v>-19.99279</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>-26.183323</v>
+        <v>-28.493858</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>-61.665829</v>
+        <v>-60.707027</v>
       </c>
       <c r="T3" s="3" t="n">
-        <v>-46.64986</v>
+        <v>-50.254475</v>
       </c>
       <c r="U3" s="3" t="n">
-        <v>45.429413</v>
+        <v>-99.941132</v>
       </c>
       <c r="V3" s="3" t="n">
-        <v>99.93328099999999</v>
+        <v>99.94517500000001</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>99.866264</v>
+        <v>99.900192</v>
       </c>
       <c r="X3" s="3" t="n">
-        <v>99.455978</v>
+        <v>99.602097</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>99.751839</v>
+        <v>99.815819</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 12:20:27</t>
+          <t>2026-05-13 12:35:33</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>12129.817383</v>
+        <v>13254.836914</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>28145.224609</v>
+        <v>33627.851562</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>-13728.067383</v>
+        <v>-17223.724609</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>26546.976562</v>
+        <v>29658.962891</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>45248.351562</v>
+        <v>52384.945312</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>37213.164062</v>
+        <v>44790.078125</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>-27128.556641</v>
+        <v>-31032.564453</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>55332.960938</v>
+        <v>66142.460938</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>46828.183594</v>
+        <v>54046.859375</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>46698.988281</v>
+        <v>56036.632812</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>30509.039062</v>
+        <v>35621.082031</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>124036.210938</v>
+        <v>145704.578125</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-25.902813</v>
+        <v>-24.524712</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-60.269455</v>
+        <v>-60.010475</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>-44.996723</v>
+        <v>-48.352615</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>-21.401566</v>
+        <v>-20.368347</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>-26.183323</v>
+        <v>-25.454176</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>-61.665829</v>
+        <v>-60.723473</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>-46.64986</v>
+        <v>-49.96434</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>45.429413</v>
+        <v>-99.89473700000001</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>99.93328099999999</v>
+        <v>99.946594</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>99.866264</v>
+        <v>99.901932</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>99.455978</v>
+        <v>99.568054</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>99.751839</v>
+        <v>99.805519</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 12:20:58</t>
+          <t>2026-05-13 12:35:49</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>14026.757812</v>
+        <v>13148.261719</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>29678.408203</v>
+        <v>32924.550781</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>-15460.938477</v>
+        <v>-16869.222656</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>28244.226562</v>
+        <v>29203.589844</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>45444.019531</v>
+        <v>52064.472656</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>37419.769531</v>
+        <v>44570.199219</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-27646.005859</v>
+        <v>-31210.470703</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>55217.78125</v>
+        <v>65424.203125</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>47587.296875</v>
+        <v>53681.796875</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>47815.6875</v>
+        <v>55427.847656</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>31832.904297</v>
+        <v>35610.800781</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>127235.890625</v>
+        <v>144720.4375</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-29.475843</v>
+        <v>-24.492962</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-62.068352</v>
+        <v>-59.400738</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>-48.569046</v>
+        <v>-47.371086</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>-22.276114</v>
+        <v>-20.244286</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>-26.435194</v>
+        <v>-25.454176</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-61.973316</v>
+        <v>-60.723473</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-47.265442</v>
+        <v>-49.96434</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>-99.887108</v>
+        <v>-99.89473700000001</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>99.93452499999999</v>
+        <v>99.946594</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>99.865082</v>
+        <v>99.901932</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>99.44972199999999</v>
+        <v>99.568054</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>99.749779</v>
+        <v>99.805519</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:36:04</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>13069.265625</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>32434.119141</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>-16732.544922</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>28770.837891</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>51725.585938</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>44310.117188</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>-31324.617188</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>64711.085938</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>53329.445312</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>54944.148438</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>35624.074219</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>143897.671875</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-24.50666</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-59.031071</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>-46.969769</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>-19.91456</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>-25.454176</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>-60.723473</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>-49.96434</v>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>-99.89473700000001</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>99.946594</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>99.901932</v>
+      </c>
+      <c r="X6" s="3" t="n">
+        <v>99.568054</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>99.805519</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:36:19</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>14083.036133</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>33610.554688</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>-17737.341797</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>29956.248047</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>52063.351562</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>44581.605469</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>-31501.214844</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>65143.738281</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>53931.777344</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>55863.777344</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>36272.3125</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>146067.875</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-26.112686</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-60.165207</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>-48.900497</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>-20.506704</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>-24.511864</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>-58.682487</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>-46.764397</v>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>-99.7565</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>99.946533</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>99.892426</v>
+      </c>
+      <c r="X7" s="3" t="n">
+        <v>99.556732</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>99.79856100000001</v>
       </c>
     </row>
   </sheetData>
@@ -8096,7 +8924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -8185,76 +9013,126 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 12:19:57</t>
+          <t>2026-05-13 12:35:18</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>7694584.742669</v>
+        <v>7694592.58693</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>-185.540567</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>7694399.196025</v>
+        <v>7694407.040286</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>19606959.235554</v>
+        <v>19606975.173046</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>-3.179442</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>19606956.053396</v>
+        <v>19606971.990888</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 12:20:27</t>
+          <t>2026-05-13 12:35:33</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>7694584.972552</v>
+        <v>7694592.71042</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>-185.540567</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>7694399.425908</v>
+        <v>7694407.163776</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>19606959.700831</v>
+        <v>19606975.451261</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>-3.179442</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>19606956.518673</v>
+        <v>19606972.269103</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 12:20:58</t>
+          <t>2026-05-13 12:35:49</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>7694585.21365</v>
+        <v>7694592.834381</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>-185.540567</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>7694399.667006</v>
+        <v>7694407.287737</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>19606960.184582</v>
+        <v>19606975.728219</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>-3.179442</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>19606957.002424</v>
+        <v>19606972.546062</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:36:04</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>7694592.958213</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>-185.540567</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>7694407.411569</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>19606976.005065</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>-3.179442</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>19606972.822907</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:36:19</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>7694593.084387</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>-185.540567</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>7694407.537743</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>19606976.283034</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>-3.179442</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>19606973.100876</v>
       </c>
     </row>
   </sheetData>
@@ -8269,7 +9147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -8468,166 +9346,276 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 12:19:57</t>
+          <t>2026-05-13 12:35:18</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>16.930384</v>
+        <v>18.429243</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>26830.056641</v>
+        <v>29823.472656</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>58500.984375</v>
+        <v>60045.011719</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>126226.125</v>
+        <v>137234.3125</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>16.845064</v>
+        <v>19.546124</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>27468.087891</v>
+        <v>30428.480469</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>56658.265625</v>
+        <v>64404.527344</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>125584.445312</v>
+        <v>145439</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>16.885403</v>
+        <v>19.460947</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>27570.984375</v>
+        <v>29409.765625</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>56303.5625</v>
+        <v>65287.976562</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>125802.945312</v>
+        <v>145286.078125</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>16.888569</v>
+        <v>19.300308</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>26925.490234</v>
+        <v>27244.123047</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>55329.933594</v>
+        <v>64318.171875</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>125969.625</v>
+        <v>144456.140625</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 12:20:27</t>
+          <t>2026-05-13 12:35:33</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>16.930384</v>
+        <v>18.429243</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>26830.056641</v>
+        <v>29823.472656</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>58500.984375</v>
+        <v>60045.011719</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>126226.125</v>
+        <v>137234.3125</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>16.85718</v>
+        <v>19.541069</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>27503.650391</v>
+        <v>30366.384766</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>56616.859375</v>
+        <v>64473.34375</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>125657.023438</v>
+        <v>145432.625</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>17.004322</v>
+        <v>19.40449</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>28077.533203</v>
+        <v>29354.759766</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>56731.726562</v>
+        <v>64947.445312</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>126647.601562</v>
+        <v>144768.109375</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>18.149618</v>
+        <v>18.731968</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>32995.074219</v>
+        <v>28333.84375</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>59515.640625</v>
+        <v>60917.675781</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>135239.28125</v>
+        <v>138692.8125</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 12:20:58</t>
+          <t>2026-05-13 12:35:49</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>16.930384</v>
+        <v>18.429243</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>26830.056641</v>
+        <v>29823.472656</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>58500.984375</v>
+        <v>60045.011719</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>126226.125</v>
+        <v>137234.3125</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>16.87326</v>
+        <v>19.535374</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>27547.849609</v>
+        <v>30318.277344</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>56569.511719</v>
+        <v>64535.839844</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>125764.109375</v>
+        <v>145416.9375</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>17.064043</v>
+        <v>19.499504</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>28151.140625</v>
+        <v>29911.083984</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>56035.054688</v>
+        <v>65592.125</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>127088.398438</v>
+        <v>145477.84375</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>17.027821</v>
+        <v>19.507982</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>27866.708984</v>
+        <v>30633.980469</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>49078.902344</v>
+        <v>65926.5</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>126272.078125</v>
+        <v>145659.03125</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:36:04</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>18.429243</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>29823.472656</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>60045.011719</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>137234.3125</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>19.529181</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>30269.96875</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>64584.214844</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>145392.90625</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>19.415503</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>29530.462891</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>64981.601562</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>144803.046875</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>19.487066</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>30292.074219</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>64957.203125</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>144817.265625</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:36:19</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>18.429243</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>29823.472656</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>60045.011719</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>137234.3125</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>19.527346</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>30233.238281</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>64602.261719</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>145399.4375</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>19.525829</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>29891.816406</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>64788.503906</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>145623.34375</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>19.925413</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>30594.962891</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>59800.617188</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>148451.484375</v>
       </c>
     </row>
   </sheetData>
@@ -8642,7 +9630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD5"/>
+  <dimension ref="A1:AD7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -8868,7 +9856,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 12:19:57</t>
+          <t>2026-05-13 12:35:18</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -8962,7 +9950,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 12:20:27</t>
+          <t>2026-05-13 12:35:33</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -9056,7 +10044,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 12:20:58</t>
+          <t>2026-05-13 12:35:49</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -9144,6 +10132,194 @@
         <v>0</v>
       </c>
       <c r="AD5" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:36:04</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>1403</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>304</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>202</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="3" t="n">
+        <v>154</v>
+      </c>
+      <c r="AB6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:36:19</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>1403</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>304</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>202</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="3" t="n">
+        <v>154</v>
+      </c>
+      <c r="AB7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9159,7 +10335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z5"/>
+  <dimension ref="A1:Z7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -9441,7 +10617,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 12:19:57</t>
+          <t>2026-05-13 12:35:18</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -9523,7 +10699,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 12:20:27</t>
+          <t>2026-05-13 12:35:33</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -9605,7 +10781,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 12:20:58</t>
+          <t>2026-05-13 12:35:49</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -9681,6 +10857,170 @@
         <v>0</v>
       </c>
       <c r="Z5" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:36:04</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:36:19</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9696,7 +11036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AC7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -10011,7 +11351,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 12:19:57</t>
+          <t>2026-05-13 12:35:18</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -10102,7 +11442,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 12:20:27</t>
+          <t>2026-05-13 12:35:33</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -10193,7 +11533,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 12:20:58</t>
+          <t>2026-05-13 12:35:49</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -10278,6 +11618,188 @@
         <v>0</v>
       </c>
       <c r="AC5" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:36:04</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:36:19</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="3" t="n">
         <v>0</v>
       </c>
     </row>

--- a/ab_meter_output/xlsx/ABMeter_10_16_130_51.xlsx
+++ b/ab_meter_output/xlsx/ABMeter_10_16_130_51.xlsx
@@ -5836,7 +5836,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:18</t>
+          <t>2026-05-13 12:42:59</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -5930,7 +5930,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:33</t>
+          <t>2026-05-13 12:43:30</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -6024,7 +6024,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:49</t>
+          <t>2026-05-13 12:44:00</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -6118,7 +6118,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-13 12:36:04</t>
+          <t>2026-05-13 12:44:31</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -6212,7 +6212,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-13 12:36:19</t>
+          <t>2026-05-13 12:45:01</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -6380,7 +6380,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:18</t>
+          <t>2026-05-13 12:42:59</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -6405,7 +6405,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:33</t>
+          <t>2026-05-13 12:43:30</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -6430,7 +6430,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:49</t>
+          <t>2026-05-13 12:44:00</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -6455,7 +6455,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-13 12:36:04</t>
+          <t>2026-05-13 12:44:31</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -6480,7 +6480,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-13 12:36:19</t>
+          <t>2026-05-13 12:45:01</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -6740,7 +6740,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:18</t>
+          <t>2026-05-13 12:42:59</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -6834,7 +6834,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:33</t>
+          <t>2026-05-13 12:43:30</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -6928,7 +6928,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:49</t>
+          <t>2026-05-13 12:44:00</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -7022,7 +7022,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-13 12:36:04</t>
+          <t>2026-05-13 12:44:31</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -7116,7 +7116,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-13 12:36:19</t>
+          <t>2026-05-13 12:45:01</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -7344,7 +7344,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:18</t>
+          <t>2026-05-13 12:42:59</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -7393,7 +7393,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:33</t>
+          <t>2026-05-13 12:43:30</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -7442,7 +7442,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:49</t>
+          <t>2026-05-13 12:44:00</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -7491,7 +7491,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-13 12:36:04</t>
+          <t>2026-05-13 12:44:31</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -7540,7 +7540,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-13 12:36:19</t>
+          <t>2026-05-13 12:45:01</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -7859,71 +7859,71 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:18</t>
+          <t>2026-05-13 12:42:59</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>21.405926</v>
+        <v>21.209766</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>22.166044</v>
+        <v>21.528526</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>14.442257</v>
+        <v>14.344177</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>0.004597</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>19.338076</v>
+        <v>19.027491</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>9.440186000000001</v>
+        <v>9.207246</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>14.393217</v>
+        <v>14.123498</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>152.467529</v>
+        <v>153.395477</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>4332.708984</v>
+        <v>4308.125977</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>4298.211914</v>
+        <v>4275.412109</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>4314.562012</v>
+        <v>4292.240234</v>
       </c>
       <c r="M3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>4315.160645</v>
+        <v>4291.92627</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>4314.286621</v>
+        <v>4291.053223</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>33.360958</v>
+        <v>31.812056</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.773267</v>
+        <v>0.741358</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>2502.071777</v>
+        <v>2488.369873</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>2490.514648</v>
+        <v>2476.574463</v>
       </c>
       <c r="T3" s="3" t="n">
-        <v>2480.625488</v>
+        <v>2467.99585</v>
       </c>
       <c r="U3" s="3" t="n">
-        <v>2491.070557</v>
+        <v>2477.646729</v>
       </c>
       <c r="V3" s="3" t="n">
-        <v>60.020504</v>
+        <v>59.986324</v>
       </c>
       <c r="W3" s="3" t="n">
         <v>2</v>
@@ -7932,71 +7932,71 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:33</t>
+          <t>2026-05-13 12:43:30</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>21.626606</v>
+        <v>21.785986</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>22.533844</v>
+        <v>22.166044</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.344177</v>
+        <v>14.761017</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0.004597</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>19.501543</v>
+        <v>19.571016</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>9.648604000000001</v>
+        <v>9.476965</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>14.564857</v>
+        <v>14.515817</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>150.952988</v>
+        <v>153.169464</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>4326.887207</v>
+        <v>4318.813477</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>4294.750977</v>
+        <v>4286.632812</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>4309.907715</v>
+        <v>4305.250488</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>4310.515625</v>
+        <v>4303.565918</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>4309.639648</v>
+        <v>4302.729492</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>31.931202</v>
+        <v>31.573763</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.7409249999999999</v>
+        <v>0.733808</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>2498.616455</v>
+        <v>2495.399414</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>2487.893311</v>
+        <v>2482.531738</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>2478.599854</v>
+        <v>2475.263916</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>2488.369873</v>
+        <v>2484.398438</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>60.023434</v>
+        <v>60.003902</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>2</v>
@@ -8005,71 +8005,71 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:49</t>
+          <t>2026-05-13 12:44:00</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>21.589827</v>
+        <v>21.663385</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>22.448025</v>
+        <v>22.006666</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>14.331918</v>
+        <v>15.092036</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>0.004597</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>19.456589</v>
+        <v>19.587362</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>9.611825</v>
+        <v>9.305326000000001</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>14.515817</v>
+        <v>14.454517</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>151.020401</v>
+        <v>155.335968</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>4326.411621</v>
+        <v>4319.760742</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>4293.199707</v>
+        <v>4288.90332</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>4310.743652</v>
+        <v>4306.565918</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>4310.118652</v>
+        <v>4305.07666</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>4309.282227</v>
+        <v>4304.15918</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>32.288639</v>
+        <v>30.620592</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.749281</v>
+        <v>0.711419</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>2499.093018</v>
+        <v>2495.75708</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>2486.821045</v>
+        <v>2483.484863</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>2478.480713</v>
+        <v>2476.455322</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>2488.131592</v>
+        <v>2485.232422</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>60.026363</v>
+        <v>60.020504</v>
       </c>
       <c r="W5" s="3" t="n">
         <v>2</v>
@@ -8078,68 +8078,68 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-13 12:36:04</t>
+          <t>2026-05-13 12:44:31</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>21.307846</v>
+        <v>21.565306</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>22.031185</v>
+        <v>21.847286</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>14.393217</v>
+        <v>14.577117</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>0.004597</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>19.244081</v>
+        <v>19.329903</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>9.391145</v>
+        <v>9.366625000000001</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>14.319657</v>
+        <v>14.331918</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>152.480423</v>
+        <v>153.010468</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>4324.750488</v>
+        <v>4316.197266</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>4290.931641</v>
+        <v>4286.515625</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>4309.071777</v>
+        <v>4304.178711</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>4308.251465</v>
+        <v>4302.297363</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>4307.375977</v>
+        <v>4301.418945</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>32.64608</v>
+        <v>30.144007</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.757911</v>
+        <v>0.700792</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>2498.259033</v>
+        <v>2493.850586</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>2485.748779</v>
+        <v>2481.697754</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>2477.051025</v>
+        <v>2475.263916</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>2487.019531</v>
+        <v>2483.604248</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>60.017574</v>
@@ -8151,71 +8151,71 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-13 12:36:19</t>
+          <t>2026-05-13 12:45:01</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>21.589827</v>
+        <v>21.835026</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>22.484804</v>
+        <v>22.251865</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>14.626157</v>
+        <v>14.908136</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.004291</v>
+        <v>0.004597</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>19.566929</v>
+        <v>19.665009</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>9.550525</v>
+        <v>9.476965</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>14.564857</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>152.503204</v>
+        <v>153.686935</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>4324.274902</v>
+        <v>4312.515625</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>4292.363281</v>
+        <v>4283.889648</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>4308.952637</v>
+        <v>4300.239746</v>
       </c>
       <c r="M7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>4308.530762</v>
+        <v>4298.881348</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>4307.614258</v>
+        <v>4297.963379</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>31.692909</v>
+        <v>29.667421</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.735742</v>
+        <v>0.690267</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>2497.782471</v>
+        <v>2491.586914</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>2486.106201</v>
+        <v>2479.9104</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>2477.765869</v>
+        <v>2473.476562</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>2487.218018</v>
+        <v>2481.657959</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>60.017574</v>
+        <v>60.015621</v>
       </c>
       <c r="W7" s="3" t="n">
         <v>2</v>
@@ -8520,396 +8520,396 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:18</t>
+          <t>2026-05-13 12:42:59</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>12998.02832</v>
+        <v>13884.283203</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>33183.695312</v>
+        <v>31178.216797</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>-16949.527344</v>
+        <v>-15828.902344</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>29232.195312</v>
+        <v>29233.597656</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>52436.175781</v>
+        <v>50529.886719</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>44996.6875</v>
+        <v>42524.429688</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-31331.910156</v>
+        <v>-31647.333984</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>66100.953125</v>
+        <v>61406.976562</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>54014.140625</v>
+        <v>52406.636719</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>55937.632812</v>
+        <v>52745.152344</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>35739.71875</v>
+        <v>35493.847656</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>145691.5</v>
+        <v>140645.640625</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>-24.064121</v>
+        <v>-26.49337</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>-59.32267</v>
+        <v>-59.111057</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>-47.424908</v>
+        <v>-44.596184</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>-19.99279</v>
+        <v>-20.849566</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>-28.493858</v>
+        <v>-27.459887</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>-60.707027</v>
+        <v>-59.867256</v>
       </c>
       <c r="T3" s="3" t="n">
-        <v>-50.254475</v>
+        <v>-45.619194</v>
       </c>
       <c r="U3" s="3" t="n">
-        <v>-99.941132</v>
+        <v>-99.825867</v>
       </c>
       <c r="V3" s="3" t="n">
-        <v>99.94517500000001</v>
+        <v>99.94244399999999</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>99.900192</v>
+        <v>99.892876</v>
       </c>
       <c r="X3" s="3" t="n">
-        <v>99.602097</v>
+        <v>99.580147</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>99.815819</v>
+        <v>99.805153</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:33</t>
+          <t>2026-05-13 12:43:30</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>13254.836914</v>
+        <v>14082.101562</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>33627.851562</v>
+        <v>32227.980469</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>-17223.724609</v>
+        <v>-16118.244141</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>29658.962891</v>
+        <v>30191.837891</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>52384.945312</v>
+        <v>51659.957031</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>44790.078125</v>
+        <v>43211.273438</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>-31032.564453</v>
+        <v>-31664.253906</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>66142.460938</v>
+        <v>63206.980469</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>54046.859375</v>
+        <v>53531</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>56036.632812</v>
+        <v>53919.25</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>35621.082031</v>
+        <v>35646.980469</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>145704.578125</v>
+        <v>143097.234375</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-24.524712</v>
+        <v>-26.306442</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-60.010475</v>
+        <v>-59.770821</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>-48.352615</v>
+        <v>-45.216297</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>-20.368347</v>
+        <v>-21.113466</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>-25.454176</v>
+        <v>-27.459887</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>-60.723473</v>
+        <v>-59.867256</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>-49.96434</v>
+        <v>-45.619194</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>-99.89473700000001</v>
+        <v>-99.825867</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>99.946594</v>
+        <v>99.94244399999999</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>99.901932</v>
+        <v>99.892876</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>99.568054</v>
+        <v>99.580147</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>99.805519</v>
+        <v>99.805153</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:49</t>
+          <t>2026-05-13 12:44:00</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>13148.261719</v>
+        <v>15326.597656</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>32924.550781</v>
+        <v>32807.316406</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>-16869.222656</v>
+        <v>-17349.371094</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>29203.589844</v>
+        <v>30784.542969</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>52064.472656</v>
+        <v>51768.773438</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>44570.199219</v>
+        <v>43585.785156</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-31210.470703</v>
+        <v>-32422.058594</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>65424.203125</v>
+        <v>62932.503906</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>53681.796875</v>
+        <v>54013.019531</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>55427.847656</v>
+        <v>54600.117188</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>35610.800781</v>
+        <v>36922.886719</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>144720.4375</v>
+        <v>145536.03125</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-24.492962</v>
+        <v>-28.375748</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-59.400738</v>
+        <v>-60.086536</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>-47.371086</v>
+        <v>-46.988121</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>-20.244286</v>
+        <v>-21.368359</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>-25.454176</v>
+        <v>-26.722082</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-60.723473</v>
+        <v>-60.243839</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-49.96434</v>
+        <v>-46.081749</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>-99.89473700000001</v>
+        <v>-99.83026099999999</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>99.946594</v>
+        <v>99.94561</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>99.901932</v>
+        <v>99.896843</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>99.568054</v>
+        <v>99.569382</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>99.805519</v>
+        <v>99.80394699999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-13 12:36:04</t>
+          <t>2026-05-13 12:44:31</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>13069.265625</v>
+        <v>15538.71875</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>32434.119141</v>
+        <v>32979.425781</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>-16732.544922</v>
+        <v>-17115.466797</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>28770.837891</v>
+        <v>31402.677734</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>51725.585938</v>
+        <v>51834.214844</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>44310.117188</v>
+        <v>43159.949219</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-31324.617188</v>
+        <v>-32264.908203</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>64711.085938</v>
+        <v>62729.257812</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>53329.445312</v>
+        <v>54124.640625</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>54944.148438</v>
+        <v>54373.035156</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>35624.074219</v>
+        <v>36690.851562</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>143897.671875</v>
+        <v>145188.53125</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-24.50666</v>
+        <v>-28.709139</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-59.031071</v>
+        <v>-60.654011</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-46.969769</v>
+        <v>-46.647778</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>-19.91456</v>
+        <v>-21.516445</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-25.454176</v>
+        <v>-26.722082</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-60.723473</v>
+        <v>-60.243839</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-49.96434</v>
+        <v>-46.081749</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-99.89473700000001</v>
+        <v>-99.83026099999999</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>99.946594</v>
+        <v>99.94561</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>99.901932</v>
+        <v>99.896843</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>99.568054</v>
+        <v>99.569382</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>99.805519</v>
+        <v>99.80394699999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-13 12:36:19</t>
+          <t>2026-05-13 12:45:01</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>14083.036133</v>
+        <v>16719.832031</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>33610.554688</v>
+        <v>34740.0625</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>-17737.341797</v>
+        <v>-18680.435547</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>29956.248047</v>
+        <v>32779.460938</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>52063.351562</v>
+        <v>52089.808594</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>44581.605469</v>
+        <v>43458.171875</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-31501.214844</v>
+        <v>-32098.408203</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>65143.738281</v>
+        <v>63449.578125</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>53931.777344</v>
+        <v>54734.644531</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>55863.777344</v>
+        <v>55674.371094</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>36272.3125</v>
+        <v>37299.453125</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>146067.875</v>
+        <v>147708.46875</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-26.112686</v>
+        <v>-30.547073</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-60.165207</v>
+        <v>-62.398663</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>-48.900497</v>
+        <v>-50.082336</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>-20.506704</v>
+        <v>-22.190203</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>-24.511864</v>
+        <v>-26.215488</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-58.682487</v>
+        <v>-59.840096</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-46.764397</v>
+        <v>-45.117847</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>-99.7565</v>
+        <v>-99.78675800000001</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>99.946533</v>
+        <v>99.943146</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>99.892426</v>
+        <v>99.89334100000001</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>99.556732</v>
+        <v>99.558548</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>99.79856100000001</v>
+        <v>99.79834</v>
       </c>
     </row>
   </sheetData>
@@ -9013,126 +9013,126 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:18</t>
+          <t>2026-05-13 12:42:59</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>7694592.58693</v>
+        <v>7694596.437233</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>-185.540567</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>7694407.040286</v>
+        <v>7694410.890589</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>19606975.173046</v>
+        <v>19606983.252204</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>-3.179442</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>19606971.990888</v>
+        <v>19606980.070047</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:33</t>
+          <t>2026-05-13 12:43:30</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>7694592.71042</v>
+        <v>7694596.69532</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>-185.540567</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>7694407.163776</v>
+        <v>7694411.148676</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>19606975.451261</v>
+        <v>19606983.785144</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>-3.179442</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>19606972.269103</v>
+        <v>19606980.602987</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:49</t>
+          <t>2026-05-13 12:44:00</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>7694592.834381</v>
+        <v>7694596.955512</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>-185.540567</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>7694407.287737</v>
+        <v>7694411.408868</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>19606975.728219</v>
+        <v>19606984.317545</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>-3.179442</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>19606972.546062</v>
+        <v>19606981.135387</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-13 12:36:04</t>
+          <t>2026-05-13 12:44:31</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>7694592.958213</v>
+        <v>7694597.21441</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>-185.540567</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>7694407.411569</v>
+        <v>7694411.667766</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>19606976.005065</v>
+        <v>19606984.844738</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>-3.179442</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>19606972.822907</v>
+        <v>19606981.662581</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-13 12:36:19</t>
+          <t>2026-05-13 12:45:01</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>7694593.084387</v>
+        <v>7694597.48</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>-185.540567</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>7694407.537743</v>
+        <v>7694411.933356</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>19606976.283034</v>
+        <v>19606985.379948</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>-3.179442</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>19606973.100876</v>
+        <v>19606982.19779</v>
       </c>
     </row>
   </sheetData>
@@ -9346,7 +9346,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:18</t>
+          <t>2026-05-13 12:42:59</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -9362,46 +9362,46 @@
         <v>137234.3125</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>19.546124</v>
+        <v>19.401037</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>30428.480469</v>
+        <v>30198.203125</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>64404.527344</v>
+        <v>63574.117188</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>145439</v>
+        <v>144592.640625</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>19.460947</v>
+        <v>19.339186</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>29409.765625</v>
+        <v>30173.017578</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>65287.976562</v>
+        <v>63316.167969</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>145286.078125</v>
+        <v>144069.859375</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>19.300308</v>
+        <v>19.236126</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>27244.123047</v>
+        <v>29799.470703</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>64318.171875</v>
+        <v>63347.03125</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>144456.140625</v>
+        <v>143282.171875</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:33</t>
+          <t>2026-05-13 12:43:30</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -9417,46 +9417,46 @@
         <v>137234.3125</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>19.541069</v>
+        <v>19.396725</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>30366.384766</v>
+        <v>30206.207031</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>64473.34375</v>
+        <v>63541.625</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>145432.625</v>
+        <v>144560.5625</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>19.40449</v>
+        <v>19.381994</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>29354.759766</v>
+        <v>30222.574219</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>64947.445312</v>
+        <v>63407.71875</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>144768.109375</v>
+        <v>144461.5</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>18.731968</v>
+        <v>19.373041</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>28333.84375</v>
+        <v>30208.667969</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>60917.675781</v>
+        <v>63349.136719</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>138692.8125</v>
+        <v>144406.796875</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:49</t>
+          <t>2026-05-13 12:44:00</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -9472,46 +9472,46 @@
         <v>137234.3125</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>19.535374</v>
+        <v>19.39431</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>30318.277344</v>
+        <v>30225.474609</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>64535.839844</v>
+        <v>63514.117188</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>145416.9375</v>
+        <v>144544.9375</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>19.499504</v>
+        <v>19.390987</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>29911.083984</v>
+        <v>30261.636719</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>65592.125</v>
+        <v>63414.691406</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>145477.84375</v>
+        <v>144529.25</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>19.507982</v>
+        <v>19.399109</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>30633.980469</v>
+        <v>30254.347656</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>65926.5</v>
+        <v>63422.710938</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>145659.03125</v>
+        <v>144586.828125</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-13 12:36:04</t>
+          <t>2026-05-13 12:44:31</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -9527,46 +9527,46 @@
         <v>137234.3125</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>19.529181</v>
+        <v>19.393129</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>30269.96875</v>
+        <v>30246.1875</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>64584.214844</v>
+        <v>63485.335938</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>145392.90625</v>
+        <v>144536.40625</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>19.415503</v>
+        <v>19.392897</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>29530.462891</v>
+        <v>30312.205078</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>64981.601562</v>
+        <v>63443.683594</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>144803.046875</v>
+        <v>144534</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>19.487066</v>
+        <v>19.399469</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>30292.074219</v>
+        <v>30341.392578</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>64957.203125</v>
+        <v>63436.542969</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>144817.265625</v>
+        <v>144581.15625</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-13 12:36:19</t>
+          <t>2026-05-13 12:45:01</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -9582,40 +9582,40 @@
         <v>137234.3125</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>19.527346</v>
+        <v>19.392851</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>30233.238281</v>
+        <v>30274.505859</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>64602.261719</v>
+        <v>63453.066406</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>145399.4375</v>
+        <v>144532.28125</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>19.525829</v>
+        <v>19.385532</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>29891.816406</v>
+        <v>30278.580078</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>64788.503906</v>
+        <v>63385.34375</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>145623.34375</v>
+        <v>144472.671875</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>19.925413</v>
+        <v>19.380207</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>30594.962891</v>
+        <v>30252.929688</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>59800.617188</v>
+        <v>63366.628906</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>148451.484375</v>
+        <v>144431.375</v>
       </c>
     </row>
   </sheetData>
@@ -9856,7 +9856,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:18</t>
+          <t>2026-05-13 12:42:59</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -9950,7 +9950,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:33</t>
+          <t>2026-05-13 12:43:30</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -10044,7 +10044,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:49</t>
+          <t>2026-05-13 12:44:00</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -10138,7 +10138,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-13 12:36:04</t>
+          <t>2026-05-13 12:44:31</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -10232,7 +10232,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-13 12:36:19</t>
+          <t>2026-05-13 12:45:01</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -10617,7 +10617,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:18</t>
+          <t>2026-05-13 12:42:59</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -10699,7 +10699,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:33</t>
+          <t>2026-05-13 12:43:30</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -10781,7 +10781,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:49</t>
+          <t>2026-05-13 12:44:00</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -10863,7 +10863,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-13 12:36:04</t>
+          <t>2026-05-13 12:44:31</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -10945,7 +10945,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-13 12:36:19</t>
+          <t>2026-05-13 12:45:01</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -11351,7 +11351,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:18</t>
+          <t>2026-05-13 12:42:59</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -11442,7 +11442,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:33</t>
+          <t>2026-05-13 12:43:30</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -11533,7 +11533,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:49</t>
+          <t>2026-05-13 12:44:00</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -11624,7 +11624,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-13 12:36:04</t>
+          <t>2026-05-13 12:44:31</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -11715,7 +11715,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-13 12:36:19</t>
+          <t>2026-05-13 12:45:01</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
